--- a/光伏配储项目/电价数据/2026/建云站.xlsx
+++ b/光伏配储项目/电价数据/2026/建云站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50996</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74136</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57092</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57408</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49842</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45436</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11303</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09214</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09887</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08412</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10805</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08641</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.10392</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.10595</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.08921</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08953</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07709000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.05379</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00501</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14853</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24338</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26795</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20338</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07778</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13294</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26414</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18034</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5239400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.84702</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.58199</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43166</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44083</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.59097</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79264</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63452</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.71413</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.79538</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65576</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6081599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.64359</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.58849</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5807899999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63122</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6010700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42568</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6838099999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.64866</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.76328</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.17152</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8230599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52601</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5195</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50737</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49082</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50215</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59814</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.68268</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41015</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50173</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14897</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.03771</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7619400000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.89416</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.75015</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10301</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25779</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.53234</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6553300000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.50644</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6852999999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.75025</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75722</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.49004</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8090900000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.48769</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.89276</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45257</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5963999999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33454</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52722</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48763</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47388</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19274</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49861</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.24679</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.40926</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.44239</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.51219</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5881900000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.45717</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43519</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34256</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13786</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.15342</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.21744</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05775</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.05302</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11673</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.15301</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.16411</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.49255</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05115</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11807</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.20856</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23174</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22884</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24617</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.2164</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27429</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14651</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55849</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45286</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44197</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29683</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04675</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04414</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04794</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04888</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04828</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03558</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04757</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04221</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03949</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04593999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04304</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04239</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05383</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05571</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>5.999999999999999e-05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15319</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04537</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10503</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.42866</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35112</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6706299999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44676</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04327</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04682</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04567</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03387</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.0005600000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03936</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0433</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04147</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04446</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04724</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04755</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20031</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14312</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33593</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31833</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15895</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17132</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14802</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15975</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15894</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23672</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21436</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26941</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92032</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49451</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91716</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.87222</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30118</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8965599999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63315</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19599</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87315</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5493899999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33998</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03918</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5399400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79876</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5308200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78079</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78374</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87773</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87795</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50045</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40932</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21642</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87917</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63119</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54067</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58728</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5962799999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60237</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6684</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46601</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5780299999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8764500000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6342000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85677</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8386699999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8604700000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.44933</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35351</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93299</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47009</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.49645</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41016</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16503</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19942</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20647</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43603</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59778</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89039</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.31663</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.12416</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6920700000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7799700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64342</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57585</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42094</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49633</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43145</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4982</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5553899999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.18837</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25683</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5760599999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46052</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.75744</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32448</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28677</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14911</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16064</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14723</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14709</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26745</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.15015</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26522</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14853</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13209</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11673</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10822</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14417</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14884</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44734</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44196</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43668</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3492</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5349299999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46473</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29108</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34968</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.68538</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7785</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47703</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34988</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26526</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14689</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19902</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25739</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14991</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.60795</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6595800000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6866100000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48867</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.73865</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5275299999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8864500000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47005</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48265</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48352</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36011</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49113</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49483</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44657</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.57947</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46411</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52108</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6408200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15696</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.54106</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.78347</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.80075</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.9106000000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7070299999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8041200000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.60112</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.55469</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.92843</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8515499999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6304299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.70696</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45336</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47193</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50687</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47815</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49366</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5658300000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46883</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43274</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40718</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46416</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1809</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36556</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27128</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22817</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23065</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25039</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13971</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04334</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24836</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23201</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35059</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24891</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17058</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21046</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00031</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02777</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01461</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03969</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02171</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02686</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03201</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.12164</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00277</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03314</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17086</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20112</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.1516</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5872999999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.17789</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24667</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26182</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23044</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25763</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25342</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.17513</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.65185</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.65389</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6681900000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5894199999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09290000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24154</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.18472</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.13297</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.13946</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.09672</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12208</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.06004</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11175</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18213</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02488</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13143</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.13672</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01292</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12089</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15264</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25391</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32378</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.06409000000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55379</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.46508</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13961</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33348</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.59476</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.53288</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.50806</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.52215</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48249</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.5268699999999999</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37547</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47827</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4674700000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5134</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5985900000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46005</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.58011</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5632200000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5260499999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.56935</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5152100000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.00815</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8814299999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.60742</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6013200000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37989</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24277</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12804</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.21629</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17889</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05656</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19475</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16284</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00288</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15425</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04848</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06208</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14708</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06994</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05281</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16948</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16347</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.53685</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38066</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9736399999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11427</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01742</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03956</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.005820000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04571</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16216</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26294</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24379</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25596</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48124</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.55945</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.59524</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37537</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6020700000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23557</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14686</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21306</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24005</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11674</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15475</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04527</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.02937</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04771</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04654999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08062999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06476000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09944</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17567</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20026</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23501</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12657</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11928</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19157</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20948</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25171</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51091</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38384</v>
       </c>
     </row>
   </sheetData>
